--- a/output/tables/manuscript/s6_table_effects_by_food_group.xlsx
+++ b/output/tables/manuscript/s6_table_effects_by_food_group.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="111" uniqueCount="84">
   <si>
-    <t>S6 Table. Effects of the climate, health, and climate + health swaps on the healthfulness and carbon footprint of food and beverage purchases, by food group, n=1,201 US adults</t>
+    <t>S5 Table. Effects of the climate, health, and climate + health swaps on the healthfulness and carbon footprint of food and beverage purchases, by food group, n=1,201 US adults</t>
   </si>
   <si>
     <t>Outcome</t>
